--- a/research/traditional_assets/database/data/malta/malta_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.06320000000000001</v>
+        <v>-0.00876</v>
       </c>
       <c r="E2">
-        <v>-0.113</v>
+        <v>-0.0624</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>48.6</v>
+        <v>12.45</v>
       </c>
       <c r="L2">
-        <v>0.1333699231613611</v>
+        <v>0.02539261676524577</v>
       </c>
       <c r="M2">
-        <v>3.22</v>
+        <v>18.87</v>
       </c>
       <c r="N2">
-        <v>0.003315485996705107</v>
+        <v>0.01851088875809299</v>
       </c>
       <c r="O2">
-        <v>0.06625514403292181</v>
+        <v>1.51566265060241</v>
       </c>
       <c r="P2">
-        <v>3.22</v>
+        <v>18.87</v>
       </c>
       <c r="Q2">
-        <v>0.003315485996705107</v>
+        <v>0.01851088875809299</v>
       </c>
       <c r="R2">
-        <v>0.06625514403292181</v>
+        <v>1.51566265060241</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>132.1</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.1295860309986266</v>
       </c>
       <c r="W2">
-        <v>0.03142502989649072</v>
+        <v>0.01938645078824031</v>
       </c>
       <c r="X2">
-        <v>0.0595867905559712</v>
+        <v>0.08290924652825907</v>
       </c>
       <c r="Y2">
-        <v>-0.02816176065948049</v>
+        <v>-0.06352279574001876</v>
       </c>
       <c r="Z2">
-        <v>0.1732021483910832</v>
+        <v>0.1657426813602867</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04347505728227393</v>
+        <v>0.06915122725637909</v>
       </c>
       <c r="AC2">
-        <v>-0.04347505728227393</v>
+        <v>-0.06915122725637909</v>
       </c>
       <c r="AD2">
-        <v>971.8</v>
+        <v>1009.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>971.8</v>
+        <v>1009.6</v>
       </c>
       <c r="AG2">
-        <v>971.8</v>
+        <v>877.5</v>
       </c>
       <c r="AH2">
-        <v>0.5001544004117344</v>
+        <v>0.4975850172498768</v>
       </c>
       <c r="AI2">
-        <v>0.3415697163544339</v>
+        <v>0.3506164264629276</v>
       </c>
       <c r="AJ2">
-        <v>0.5001544004117344</v>
+        <v>0.4625968685750435</v>
       </c>
       <c r="AK2">
-        <v>0.3415697163544339</v>
+        <v>0.319392880541603</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.06320000000000001</v>
+        <v>-0.00876</v>
       </c>
       <c r="E3">
-        <v>-0.113</v>
+        <v>-0.0624</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>21.1</v>
+        <v>22.9</v>
       </c>
       <c r="L3">
-        <v>0.1421832884097035</v>
+        <v>0.1525649566955363</v>
       </c>
       <c r="M3">
-        <v>3.22</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="N3">
-        <v>0.008559276980329612</v>
+        <v>0.03061448427212875</v>
       </c>
       <c r="O3">
-        <v>0.15260663507109</v>
+        <v>0.3655021834061135</v>
       </c>
       <c r="P3">
-        <v>3.22</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.008559276980329612</v>
+        <v>0.03061448427212875</v>
       </c>
       <c r="R3">
-        <v>0.15260663507109</v>
+        <v>0.3655021834061135</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.03998483987113891</v>
+        <v>0.03985381134702401</v>
       </c>
       <c r="X3">
-        <v>0.04756915605509328</v>
+        <v>0.08290924652825907</v>
       </c>
       <c r="Y3">
-        <v>-0.007584316183954373</v>
+        <v>-0.04305543518123506</v>
       </c>
       <c r="Z3">
-        <v>0.2460620129331786</v>
+        <v>0.2298621745788668</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04279133247630906</v>
+        <v>0.06702948478456928</v>
       </c>
       <c r="AC3">
-        <v>-0.04279133247630906</v>
+        <v>-0.06702948478456928</v>
       </c>
       <c r="AD3">
-        <v>78.40000000000001</v>
+        <v>146.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>78.40000000000001</v>
+        <v>146.9</v>
       </c>
       <c r="AG3">
-        <v>78.40000000000001</v>
+        <v>146.9</v>
       </c>
       <c r="AH3">
-        <v>0.172459304883414</v>
+        <v>0.3495122531525102</v>
       </c>
       <c r="AI3">
-        <v>0.1200612557427259</v>
+        <v>0.2276813391196528</v>
       </c>
       <c r="AJ3">
-        <v>0.172459304883414</v>
+        <v>0.3495122531525102</v>
       </c>
       <c r="AK3">
-        <v>0.1200612557427259</v>
+        <v>0.2276813391196528</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -844,87 +844,203 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>27.5</v>
+        <v>-15</v>
       </c>
       <c r="L4">
-        <v>0.1273148148148148</v>
+        <v>-0.05368647100930566</v>
       </c>
       <c r="M4">
+        <v>10.5</v>
+      </c>
+      <c r="N4">
+        <v>0.02077562326869806</v>
+      </c>
+      <c r="O4">
+        <v>-0.7</v>
+      </c>
+      <c r="P4">
+        <v>10.5</v>
+      </c>
+      <c r="Q4">
+        <v>0.02077562326869806</v>
+      </c>
+      <c r="R4">
+        <v>-0.7</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>-0.01155001155001155</v>
+      </c>
+      <c r="X4">
+        <v>0.1028404916707376</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1143905032207491</v>
+      </c>
+      <c r="Z4">
+        <v>0.1274576889740431</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06915122725637909</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06915122725637909</v>
+      </c>
+      <c r="AD4">
+        <v>745.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>745.6</v>
+      </c>
+      <c r="AG4">
+        <v>745.6</v>
+      </c>
+      <c r="AH4">
+        <v>0.5960031974420463</v>
+      </c>
+      <c r="AI4">
+        <v>0.3997640877164764</v>
+      </c>
+      <c r="AJ4">
+        <v>0.5960031974420463</v>
+      </c>
+      <c r="AK4">
+        <v>0.3997640877164764</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>APS Bank plc (MTSE:APS)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>4.55</v>
+      </c>
+      <c r="L5">
+        <v>0.07483552631578948</v>
+      </c>
+      <c r="M5">
         <v>-0</v>
       </c>
-      <c r="N4">
+      <c r="N5">
         <v>-0</v>
       </c>
-      <c r="O4">
+      <c r="O5">
         <v>-0</v>
       </c>
-      <c r="P4">
+      <c r="P5">
         <v>-0</v>
       </c>
-      <c r="Q4">
+      <c r="Q5">
         <v>-0</v>
       </c>
-      <c r="R4">
+      <c r="R5">
         <v>-0</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0.02286521992184252</v>
-      </c>
-      <c r="X4">
-        <v>0.07160442505684912</v>
-      </c>
-      <c r="Y4">
-        <v>-0.0487392051350066</v>
-      </c>
-      <c r="Z4">
-        <v>0.1439232409381663</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.0441587820882388</v>
-      </c>
-      <c r="AC4">
-        <v>-0.0441587820882388</v>
-      </c>
-      <c r="AD4">
-        <v>893.4</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>893.4</v>
-      </c>
-      <c r="AG4">
-        <v>893.4</v>
-      </c>
-      <c r="AH4">
-        <v>0.6002418704649287</v>
-      </c>
-      <c r="AI4">
-        <v>0.407554399890516</v>
-      </c>
-      <c r="AJ4">
-        <v>0.6002418704649287</v>
-      </c>
-      <c r="AK4">
-        <v>0.407554399890516</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>132.1</v>
+      </c>
+      <c r="V5">
+        <v>0.5490440565253533</v>
+      </c>
+      <c r="W5">
+        <v>0.01938645078824031</v>
+      </c>
+      <c r="X5">
+        <v>0.0818338461814255</v>
+      </c>
+      <c r="Y5">
+        <v>-0.0624473953931852</v>
+      </c>
+      <c r="Z5">
+        <v>0.5375773651635719</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06975926720013839</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06975926720013839</v>
+      </c>
+      <c r="AD5">
+        <v>117.1</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>117.1</v>
+      </c>
+      <c r="AG5">
+        <v>-15</v>
+      </c>
+      <c r="AH5">
+        <v>0.3273693038859379</v>
+      </c>
+      <c r="AI5">
+        <v>0.3171722643553629</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.06648936170212766</v>
+      </c>
+      <c r="AK5">
+        <v>-0.06326444538169548</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/malta/malta_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00876</v>
+        <v>0.0409</v>
       </c>
       <c r="E2">
-        <v>-0.0624</v>
+        <v>0.179</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>12.45</v>
+        <v>275</v>
       </c>
       <c r="L2">
-        <v>0.02539261676524577</v>
+        <v>0.3527902501603592</v>
       </c>
       <c r="M2">
-        <v>18.87</v>
+        <v>14.3</v>
       </c>
       <c r="N2">
-        <v>0.01851088875809299</v>
+        <v>0.008565438754118001</v>
       </c>
       <c r="O2">
-        <v>1.51566265060241</v>
+        <v>0.052</v>
       </c>
       <c r="P2">
-        <v>18.87</v>
+        <v>14.3</v>
       </c>
       <c r="Q2">
-        <v>0.01851088875809299</v>
+        <v>0.008565438754118001</v>
       </c>
       <c r="R2">
-        <v>1.51566265060241</v>
+        <v>0.052</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>132.1</v>
+        <v>2506.3</v>
       </c>
       <c r="V2">
-        <v>0.1295860309986266</v>
+        <v>1.501227912548667</v>
       </c>
       <c r="W2">
-        <v>0.01938645078824031</v>
+        <v>0.141280353200883</v>
       </c>
       <c r="X2">
-        <v>0.08290924652825907</v>
+        <v>0.07106146627990174</v>
       </c>
       <c r="Y2">
-        <v>-0.06352279574001876</v>
+        <v>0.07021888692098126</v>
       </c>
       <c r="Z2">
-        <v>0.1657426813602867</v>
+        <v>0.284852914306596</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06915122725637909</v>
+        <v>0.05920982879317327</v>
       </c>
       <c r="AC2">
-        <v>-0.06915122725637909</v>
+        <v>-0.05920982879317327</v>
       </c>
       <c r="AD2">
-        <v>1009.6</v>
+        <v>1227</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1009.6</v>
+        <v>1227</v>
       </c>
       <c r="AG2">
-        <v>877.5</v>
+        <v>-1279.3</v>
       </c>
       <c r="AH2">
-        <v>0.4975850172498768</v>
+        <v>0.4236147074054894</v>
       </c>
       <c r="AI2">
-        <v>0.3506164264629276</v>
+        <v>0.3660828833129457</v>
       </c>
       <c r="AJ2">
-        <v>0.4625968685750435</v>
+        <v>-3.278575089697588</v>
       </c>
       <c r="AK2">
-        <v>0.319392880541603</v>
+        <v>-1.513248166548379</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HSBC Bank Malta p.l.c. (MTSE:HSB)</t>
+          <t>APS Bank plc (MTSE:APS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,12 +709,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.00876</v>
-      </c>
-      <c r="E3">
-        <v>-0.0624</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -728,85 +722,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="L3">
-        <v>0.1525649566955363</v>
+        <v>0.2674285714285714</v>
       </c>
       <c r="M3">
-        <v>8.369999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03061448427212875</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.3655021834061135</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>8.369999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03061448427212875</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3655021834061135</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0</v>
+        <v>168.7</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.6933826551582408</v>
       </c>
       <c r="W3">
-        <v>0.03985381134702401</v>
+        <v>0.09701492537313433</v>
       </c>
       <c r="X3">
-        <v>0.08290924652825907</v>
+        <v>0.07106146627990174</v>
       </c>
       <c r="Y3">
-        <v>-0.04305543518123506</v>
+        <v>0.02595345909323259</v>
       </c>
       <c r="Z3">
-        <v>0.2298621745788668</v>
+        <v>0.3868258178603007</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06702948478456928</v>
+        <v>0.05734384126742403</v>
       </c>
       <c r="AC3">
-        <v>-0.06702948478456928</v>
+        <v>-0.05734384126742403</v>
       </c>
       <c r="AD3">
-        <v>146.9</v>
+        <v>151.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>146.9</v>
+        <v>151.2</v>
       </c>
       <c r="AG3">
-        <v>146.9</v>
+        <v>-17.5</v>
       </c>
       <c r="AH3">
-        <v>0.3495122531525102</v>
+        <v>0.3832699619771863</v>
       </c>
       <c r="AI3">
-        <v>0.2276813391196528</v>
+        <v>0.3390894819466248</v>
       </c>
       <c r="AJ3">
-        <v>0.3495122531525102</v>
+        <v>-0.0775022143489814</v>
       </c>
       <c r="AK3">
-        <v>0.2276813391196528</v>
+        <v>-0.06313131313131314</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -844,85 +835,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-15</v>
+        <v>181.2</v>
       </c>
       <c r="L4">
-        <v>-0.05368647100930566</v>
+        <v>0.3778148457047539</v>
       </c>
       <c r="M4">
-        <v>10.5</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.02077562326869806</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.7</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>10.5</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.02077562326869806</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0.7</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0</v>
+        <v>2337.6</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>2.550851156700131</v>
       </c>
       <c r="W4">
-        <v>-0.01155001155001155</v>
+        <v>0.1618579723090665</v>
       </c>
       <c r="X4">
-        <v>0.1028404916707376</v>
+        <v>0.07645968656159337</v>
       </c>
       <c r="Y4">
-        <v>-0.1143905032207491</v>
+        <v>0.08539828574747317</v>
       </c>
       <c r="Z4">
-        <v>0.1274576889740431</v>
+        <v>0.2571443890408021</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06915122725637909</v>
+        <v>0.05920982879317327</v>
       </c>
       <c r="AC4">
-        <v>-0.06915122725637909</v>
+        <v>-0.05920982879317327</v>
       </c>
       <c r="AD4">
-        <v>745.6</v>
+        <v>900.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>745.6</v>
+        <v>900.7</v>
       </c>
       <c r="AG4">
-        <v>745.6</v>
+        <v>-1436.9</v>
       </c>
       <c r="AH4">
-        <v>0.5960031974420463</v>
+        <v>0.4956799295580871</v>
       </c>
       <c r="AI4">
-        <v>0.3997640877164764</v>
+        <v>0.4107159142726858</v>
       </c>
       <c r="AJ4">
-        <v>0.5960031974420463</v>
+        <v>2.76061479346782</v>
       </c>
       <c r="AK4">
-        <v>0.3997640877164764</v>
+        <v>9.937067773167364</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -939,7 +927,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>APS Bank plc (MTSE:APS)</t>
+          <t>HSBC Bank Malta p.l.c. (MTSE:HSB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -947,6 +935,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.0409</v>
+      </c>
+      <c r="E5">
+        <v>0.179</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -960,82 +954,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>4.55</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L5">
-        <v>0.07483552631578948</v>
+        <v>0.3314500941619586</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>14.3</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.02805021577089055</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.203125</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>14.3</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02805021577089055</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.203125</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>132.1</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.5490440565253533</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.01938645078824031</v>
+        <v>0.141280353200883</v>
       </c>
       <c r="X5">
-        <v>0.0818338461814255</v>
+        <v>0.06690933029079763</v>
       </c>
       <c r="Y5">
-        <v>-0.0624473953931852</v>
+        <v>0.07437102291008538</v>
       </c>
       <c r="Z5">
-        <v>0.5375773651635719</v>
+        <v>0.3292002479851209</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06975926720013839</v>
+        <v>0.06022995439351468</v>
       </c>
       <c r="AC5">
-        <v>-0.06975926720013839</v>
+        <v>-0.06022995439351468</v>
       </c>
       <c r="AD5">
-        <v>117.1</v>
+        <v>175.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>117.1</v>
+        <v>175.1</v>
       </c>
       <c r="AG5">
-        <v>-15</v>
+        <v>175.1</v>
       </c>
       <c r="AH5">
-        <v>0.3273693038859379</v>
+        <v>0.2556577602569718</v>
       </c>
       <c r="AI5">
-        <v>0.3171722643553629</v>
+        <v>0.2456509539842873</v>
       </c>
       <c r="AJ5">
-        <v>-0.06648936170212766</v>
+        <v>0.2556577602569718</v>
       </c>
       <c r="AK5">
-        <v>-0.06326444538169548</v>
+        <v>0.2456509539842873</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/research/traditional_assets/database/data/malta/malta_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0409</v>
+        <v>0.148</v>
       </c>
       <c r="E2">
-        <v>0.179</v>
+        <v>0.206</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>275</v>
+        <v>210.6</v>
       </c>
       <c r="L2">
-        <v>0.3527902501603592</v>
+        <v>0.3996204933586338</v>
       </c>
       <c r="M2">
-        <v>14.3</v>
+        <v>47.2</v>
       </c>
       <c r="N2">
-        <v>0.008565438754118001</v>
+        <v>0.04539771087813792</v>
       </c>
       <c r="O2">
-        <v>0.052</v>
+        <v>0.2241215574548908</v>
       </c>
       <c r="P2">
-        <v>14.3</v>
+        <v>47.2</v>
       </c>
       <c r="Q2">
-        <v>0.008565438754118001</v>
+        <v>0.04539771087813792</v>
       </c>
       <c r="R2">
-        <v>0.052</v>
+        <v>0.2241215574548908</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2506.3</v>
+        <v>1229.6</v>
       </c>
       <c r="V2">
-        <v>1.501227912548667</v>
+        <v>1.18264884101183</v>
       </c>
       <c r="W2">
-        <v>0.141280353200883</v>
+        <v>0.1631167221748896</v>
       </c>
       <c r="X2">
-        <v>0.07106146627990174</v>
+        <v>0.07679520371010881</v>
       </c>
       <c r="Y2">
-        <v>0.07021888692098126</v>
+        <v>0.08632151846478081</v>
       </c>
       <c r="Z2">
-        <v>0.284852914306596</v>
+        <v>0.2623326198417044</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05920982879317327</v>
+        <v>0.06313137920949628</v>
       </c>
       <c r="AC2">
-        <v>-0.05920982879317327</v>
+        <v>-0.06313137920949628</v>
       </c>
       <c r="AD2">
-        <v>1227</v>
+        <v>706.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1227</v>
+        <v>706.3</v>
       </c>
       <c r="AG2">
-        <v>-1279.3</v>
+        <v>-523.3</v>
       </c>
       <c r="AH2">
-        <v>0.4236147074054894</v>
+        <v>0.404524627720504</v>
       </c>
       <c r="AI2">
-        <v>0.3660828833129457</v>
+        <v>0.3303091240705233</v>
       </c>
       <c r="AJ2">
-        <v>-3.278575089697588</v>
+        <v>-1.013361735089078</v>
       </c>
       <c r="AK2">
-        <v>-1.513248166548379</v>
+        <v>-0.5758776273797732</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>APS Bank plc (MTSE:APS)</t>
+          <t>Bank of Valletta p.l.c. (MTSE:BOV)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,6 +709,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.148</v>
+      </c>
+      <c r="E3">
+        <v>0.206</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -722,322 +728,90 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>23.4</v>
+        <v>210.6</v>
       </c>
       <c r="L3">
-        <v>0.2674285714285714</v>
+        <v>0.3996204933586338</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>47.2</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04539771087813792</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2241215574548908</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>47.2</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.04539771087813792</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2241215574548908</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>168.7</v>
+        <v>1229.6</v>
       </c>
       <c r="V3">
-        <v>0.6933826551582408</v>
+        <v>1.18264884101183</v>
       </c>
       <c r="W3">
-        <v>0.09701492537313433</v>
+        <v>0.1631167221748896</v>
       </c>
       <c r="X3">
-        <v>0.07106146627990174</v>
+        <v>0.07679520371010881</v>
       </c>
       <c r="Y3">
-        <v>0.02595345909323259</v>
+        <v>0.08632151846478081</v>
       </c>
       <c r="Z3">
-        <v>0.3868258178603007</v>
+        <v>0.2623326198417044</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05734384126742403</v>
+        <v>0.06313137920949628</v>
       </c>
       <c r="AC3">
-        <v>-0.05734384126742403</v>
+        <v>-0.06313137920949628</v>
       </c>
       <c r="AD3">
-        <v>151.2</v>
+        <v>706.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>151.2</v>
+        <v>706.3</v>
       </c>
       <c r="AG3">
-        <v>-17.5</v>
+        <v>-523.3</v>
       </c>
       <c r="AH3">
-        <v>0.3832699619771863</v>
+        <v>0.404524627720504</v>
       </c>
       <c r="AI3">
-        <v>0.3390894819466248</v>
+        <v>0.3303091240705233</v>
       </c>
       <c r="AJ3">
-        <v>-0.0775022143489814</v>
+        <v>-1.013361735089078</v>
       </c>
       <c r="AK3">
-        <v>-0.06313131313131314</v>
+        <v>-0.5758776273797732</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bank of Valletta p.l.c. (MTSE:BOV)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>181.2</v>
-      </c>
-      <c r="L4">
-        <v>0.3778148457047539</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>2337.6</v>
-      </c>
-      <c r="V4">
-        <v>2.550851156700131</v>
-      </c>
-      <c r="W4">
-        <v>0.1618579723090665</v>
-      </c>
-      <c r="X4">
-        <v>0.07645968656159337</v>
-      </c>
-      <c r="Y4">
-        <v>0.08539828574747317</v>
-      </c>
-      <c r="Z4">
-        <v>0.2571443890408021</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.05920982879317327</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05920982879317327</v>
-      </c>
-      <c r="AD4">
-        <v>900.7</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>900.7</v>
-      </c>
-      <c r="AG4">
-        <v>-1436.9</v>
-      </c>
-      <c r="AH4">
-        <v>0.4956799295580871</v>
-      </c>
-      <c r="AI4">
-        <v>0.4107159142726858</v>
-      </c>
-      <c r="AJ4">
-        <v>2.76061479346782</v>
-      </c>
-      <c r="AK4">
-        <v>9.937067773167364</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HSBC Bank Malta p.l.c. (MTSE:HSB)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.0409</v>
-      </c>
-      <c r="E5">
-        <v>0.179</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="L5">
-        <v>0.3314500941619586</v>
-      </c>
-      <c r="M5">
-        <v>14.3</v>
-      </c>
-      <c r="N5">
-        <v>0.02805021577089055</v>
-      </c>
-      <c r="O5">
-        <v>0.203125</v>
-      </c>
-      <c r="P5">
-        <v>14.3</v>
-      </c>
-      <c r="Q5">
-        <v>0.02805021577089055</v>
-      </c>
-      <c r="R5">
-        <v>0.203125</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0.141280353200883</v>
-      </c>
-      <c r="X5">
-        <v>0.06690933029079763</v>
-      </c>
-      <c r="Y5">
-        <v>0.07437102291008538</v>
-      </c>
-      <c r="Z5">
-        <v>0.3292002479851209</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06022995439351468</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06022995439351468</v>
-      </c>
-      <c r="AD5">
-        <v>175.1</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>175.1</v>
-      </c>
-      <c r="AG5">
-        <v>175.1</v>
-      </c>
-      <c r="AH5">
-        <v>0.2556577602569718</v>
-      </c>
-      <c r="AI5">
-        <v>0.2456509539842873</v>
-      </c>
-      <c r="AJ5">
-        <v>0.2556577602569718</v>
-      </c>
-      <c r="AK5">
-        <v>0.2456509539842873</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/malta/malta_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.148</v>
+        <v>0.133</v>
       </c>
       <c r="E2">
-        <v>0.206</v>
+        <v>0.2465</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>210.6</v>
+        <v>335</v>
       </c>
       <c r="L2">
-        <v>0.3996204933586338</v>
+        <v>0.3751399776035834</v>
       </c>
       <c r="M2">
-        <v>47.2</v>
+        <v>97.32680000000001</v>
       </c>
       <c r="N2">
-        <v>0.04539771087813792</v>
+        <v>0.05427548516618336</v>
       </c>
       <c r="O2">
-        <v>0.2241215574548908</v>
+        <v>0.2905277611940298</v>
       </c>
       <c r="P2">
-        <v>47.2</v>
+        <v>97.32680000000001</v>
       </c>
       <c r="Q2">
-        <v>0.04539771087813792</v>
+        <v>0.05427548516618336</v>
       </c>
       <c r="R2">
-        <v>0.2241215574548908</v>
+        <v>0.2905277611940298</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1229.6</v>
+        <v>1459.7</v>
       </c>
       <c r="V2">
-        <v>1.18264884101183</v>
+        <v>0.8140196297122462</v>
       </c>
       <c r="W2">
         <v>0.1631167221748896</v>
       </c>
       <c r="X2">
-        <v>0.07679520371010881</v>
+        <v>0.0767825094521436</v>
       </c>
       <c r="Y2">
-        <v>0.08632151846478081</v>
+        <v>0.08633421272274602</v>
       </c>
       <c r="Z2">
-        <v>0.2623326198417044</v>
+        <v>0.2991725015913431</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06313137920949628</v>
+        <v>0.06312382009150863</v>
       </c>
       <c r="AC2">
-        <v>-0.06313137920949628</v>
+        <v>-0.06312382009150863</v>
       </c>
       <c r="AD2">
-        <v>706.3</v>
+        <v>1040.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>706.3</v>
+        <v>1040.5</v>
       </c>
       <c r="AG2">
-        <v>-523.3</v>
+        <v>-419.1999999999998</v>
       </c>
       <c r="AH2">
-        <v>0.404524627720504</v>
+        <v>0.3671877756996154</v>
       </c>
       <c r="AI2">
-        <v>0.3303091240705233</v>
+        <v>0.304284252083638</v>
       </c>
       <c r="AJ2">
-        <v>-1.013361735089078</v>
+        <v>-0.3050946142649197</v>
       </c>
       <c r="AK2">
-        <v>-0.5758776273797732</v>
+        <v>-0.2138993774874986</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,117 +701,355 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>APS Bank plc (MTSE:APS)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>18.3</v>
+      </c>
+      <c r="L3">
+        <v>0.2150411280846064</v>
+      </c>
+      <c r="M3">
+        <v>12.5268</v>
+      </c>
+      <c r="N3">
+        <v>0.05691412994093595</v>
+      </c>
+      <c r="O3">
+        <v>0.6845245901639345</v>
+      </c>
+      <c r="P3">
+        <v>12.5268</v>
+      </c>
+      <c r="Q3">
+        <v>0.05691412994093595</v>
+      </c>
+      <c r="R3">
+        <v>0.6845245901639345</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>230.1</v>
+      </c>
+      <c r="V3">
+        <v>1.045433893684689</v>
+      </c>
+      <c r="W3">
+        <v>0.06519415746348416</v>
+      </c>
+      <c r="X3">
+        <v>0.07742225580238744</v>
+      </c>
+      <c r="Y3">
+        <v>-0.01222809833890329</v>
+      </c>
+      <c r="Z3">
+        <v>0.3233282674772036</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.06132163925661187</v>
+      </c>
+      <c r="AC3">
+        <v>-0.06132163925661187</v>
+      </c>
+      <c r="AD3">
+        <v>159.6</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>159.6</v>
+      </c>
+      <c r="AG3">
+        <v>-70.5</v>
+      </c>
+      <c r="AH3">
+        <v>0.4203318409270477</v>
+      </c>
+      <c r="AI3">
+        <v>0.3258472846059616</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.4712566844919786</v>
+      </c>
+      <c r="AK3">
+        <v>-0.2714670773969965</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Bank of Valletta p.l.c. (MTSE:BOV)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>0.148</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>0.206</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>210.6</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>0.3996204933586338</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <v>47.2</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>0.04539771087813792</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>0.2241215574548908</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>47.2</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>0.04539771087813792</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>0.2241215574548908</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>1229.6</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>1.18264884101183</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>0.1631167221748896</v>
       </c>
-      <c r="X3">
-        <v>0.07679520371010881</v>
-      </c>
-      <c r="Y3">
-        <v>0.08632151846478081</v>
-      </c>
-      <c r="Z3">
+      <c r="X4">
+        <v>0.0767825094521436</v>
+      </c>
+      <c r="Y4">
+        <v>0.08633421272274602</v>
+      </c>
+      <c r="Z4">
         <v>0.2623326198417044</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.06313137920949628</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06313137920949628</v>
-      </c>
-      <c r="AD3">
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06312382009150863</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06312382009150863</v>
+      </c>
+      <c r="AD4">
         <v>706.3</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>706.3</v>
       </c>
-      <c r="AG3">
+      <c r="AG4">
         <v>-523.3</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.404524627720504</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.3303091240705233</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>-1.013361735089078</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>-0.5758776273797732</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HSBC Bank Malta p.l.c. (MTSE:HSB)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.118</v>
+      </c>
+      <c r="E5">
+        <v>0.287</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>106.1</v>
+      </c>
+      <c r="L5">
+        <v>0.3777144891420434</v>
+      </c>
+      <c r="M5">
+        <v>37.6</v>
+      </c>
+      <c r="N5">
+        <v>0.07049118860142482</v>
+      </c>
+      <c r="O5">
+        <v>0.3543826578699341</v>
+      </c>
+      <c r="P5">
+        <v>37.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.07049118860142482</v>
+      </c>
+      <c r="R5">
+        <v>0.3543826578699341</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.1973219267249395</v>
+      </c>
+      <c r="X5">
+        <v>0.07186512580906587</v>
+      </c>
+      <c r="Y5">
+        <v>0.1254568009158737</v>
+      </c>
+      <c r="Z5">
+        <v>0.3940796857463523</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.0647510618820365</v>
+      </c>
+      <c r="AC5">
+        <v>-0.0647510618820365</v>
+      </c>
+      <c r="AD5">
+        <v>174.6</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>174.6</v>
+      </c>
+      <c r="AG5">
+        <v>174.6</v>
+      </c>
+      <c r="AH5">
+        <v>0.2466101694915254</v>
+      </c>
+      <c r="AI5">
+        <v>0.2206216830932525</v>
+      </c>
+      <c r="AJ5">
+        <v>0.2466101694915254</v>
+      </c>
+      <c r="AK5">
+        <v>0.2206216830932525</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>
